--- a/reports/一级子公司A_利润表_2026-06.xlsx
+++ b/reports/一级子公司A_利润表_2026-06.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>181730071</v>
+        <v>186008666</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>177068363</v>
+        <v>177356019</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>975333309</v>
+        <v>975420793</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>721249</v>
+        <v>717941</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4076896</v>
+        <v>4080047</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>627454</v>
+        <v>622619</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>3536834</v>
+        <v>3538451</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>530140</v>
+        <v>527867</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2996889</v>
+        <v>2997107</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>486965</v>
+        <v>486243</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2757625</v>
+        <v>2755918</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>265576</v>
+        <v>264781</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1498834</v>
+        <v>1497134</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>212552</v>
+        <v>212293</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1198822</v>
+        <v>1197415</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>178886135</v>
+        <v>183176922</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>174224427</v>
+        <v>174524275</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>89673307</v>
+        <v>90094638</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>481827564</v>
+        <v>481403018</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1644714</v>
+        <v>1653427</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>9290929</v>
+        <v>9287753</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1481442</v>
+        <v>1491387</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>8392327</v>
+        <v>8395850</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>79655759</v>
+        <v>79534801</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>449743605</v>
+        <v>450216693</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1704582</v>
+        <v>1694761</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>9590751</v>
+        <v>9604136</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>741340</v>
+        <v>740657</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4195462</v>
+        <v>4201557</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2642513</v>
+        <v>2638613</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>14988785</v>
+        <v>15000134</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1169420</v>
+        <v>1161162</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6594815</v>
+        <v>6599405</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4567694</v>
+        <v>4537795</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>25773810</v>
+        <v>25786515</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>94014</v>
+        <v>92273</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>546921</v>
+        <v>556225</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2411575</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>13657624</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1611004</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>9101724</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>121372941</v>
+        <v>130426526</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>108463371</v>
+        <v>108824865</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>106230914</v>
+        <v>106585286</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>599552856</v>
+        <v>598887565</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2232457</v>
+        <v>2239579</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>12587713</v>
+        <v>12581314</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4051316</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>22779562</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1294887</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>7293308</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>807813</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4560295</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>967265</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>5473801</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>723901</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4105548</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>481775</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2736547</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>401084</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2279612</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1854332</v>
+        <v>1846969</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>10488874</v>
+        <v>10492799</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1428791</v>
+        <v>1426011</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>8093333</v>
+        <v>8090123</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1169194</v>
+        <v>1163657</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6594885</v>
+        <v>6588957</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8819860</v>
+        <v>8798705</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>49749435</v>
+        <v>49698932</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>365853</v>
+        <v>371790</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2125844</v>
+        <v>2095418</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>700331</v>
+        <v>692499</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4076457</v>
+        <v>4135671</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>797366</v>
+        <v>692499</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4622537</v>
+        <v>4135671</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>94236</v>
+        <v>93189</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>546841</v>
+        <v>555827</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>353960</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2113222</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>707990</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3988787</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>235220</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1410154</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>176027</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1057936</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>292764</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1763429</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1003519</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5700917</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>155751</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>940125</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>116818</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>704786</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>194881</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1174050</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>136647</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>821438</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>97812</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>586520</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>78421</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>469122</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58926</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>351845</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>57513194</v>
+        <v>55204853</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>66658736</v>
+        <v>61899789</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>405036</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2278287</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>98174</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>587342</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>157001</v>
+        <v>154712</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>912009</v>
+        <v>927773</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>57356193</v>
+        <v>55455177</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5549663</v>
+        <v>5443067</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>32239937</v>
+        <v>32793553</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>51806530</v>
+        <v>50012110</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>51806530</v>
+        <v>50012110</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>51806530</v>
+        <v>50012110</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>51806530</v>
+        <v>50012110</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>51806530</v>
+        <v>50012110</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
